--- a/data/nzd0535/nzd0535.xlsx
+++ b/data/nzd0535/nzd0535.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N489"/>
+  <dimension ref="A1:N492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23918,6 +23918,150 @@
         <v>310.78</v>
       </c>
       <c r="N489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>329.07</v>
+      </c>
+      <c r="C490" t="n">
+        <v>321.65</v>
+      </c>
+      <c r="D490" t="n">
+        <v>323.79</v>
+      </c>
+      <c r="E490" t="n">
+        <v>319.96</v>
+      </c>
+      <c r="F490" t="n">
+        <v>321.49</v>
+      </c>
+      <c r="G490" t="n">
+        <v>321.04</v>
+      </c>
+      <c r="H490" t="n">
+        <v>322.14</v>
+      </c>
+      <c r="I490" t="n">
+        <v>324.48</v>
+      </c>
+      <c r="J490" t="n">
+        <v>325.64</v>
+      </c>
+      <c r="K490" t="n">
+        <v>324</v>
+      </c>
+      <c r="L490" t="n">
+        <v>311.61</v>
+      </c>
+      <c r="M490" t="n">
+        <v>313.37</v>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>328.67</v>
+      </c>
+      <c r="C491" t="n">
+        <v>321.48</v>
+      </c>
+      <c r="D491" t="n">
+        <v>323.38</v>
+      </c>
+      <c r="E491" t="n">
+        <v>320.51</v>
+      </c>
+      <c r="F491" t="n">
+        <v>321.82</v>
+      </c>
+      <c r="G491" t="n">
+        <v>321.42</v>
+      </c>
+      <c r="H491" t="n">
+        <v>321.75</v>
+      </c>
+      <c r="I491" t="n">
+        <v>323.67</v>
+      </c>
+      <c r="J491" t="n">
+        <v>324.79</v>
+      </c>
+      <c r="K491" t="n">
+        <v>323.29</v>
+      </c>
+      <c r="L491" t="n">
+        <v>310</v>
+      </c>
+      <c r="M491" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="C492" t="n">
+        <v>320.62</v>
+      </c>
+      <c r="D492" t="n">
+        <v>322.62</v>
+      </c>
+      <c r="E492" t="n">
+        <v>319.67</v>
+      </c>
+      <c r="F492" t="n">
+        <v>321.5</v>
+      </c>
+      <c r="G492" t="n">
+        <v>321.15</v>
+      </c>
+      <c r="H492" t="n">
+        <v>321.28</v>
+      </c>
+      <c r="I492" t="n">
+        <v>323.67</v>
+      </c>
+      <c r="J492" t="n">
+        <v>324.79</v>
+      </c>
+      <c r="K492" t="n">
+        <v>323.29</v>
+      </c>
+      <c r="L492" t="n">
+        <v>310</v>
+      </c>
+      <c r="M492" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="N492" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23934,7 +24078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:B548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29387,6 +29531,36 @@
       </c>
       <c r="B545" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -29555,28 +29729,28 @@
         <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1827474163472802</v>
+        <v>0.182799918777777</v>
       </c>
       <c r="J2" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K2" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06966228452057777</v>
+        <v>0.07058908171940725</v>
       </c>
       <c r="M2" t="n">
-        <v>3.653617145128026</v>
+        <v>3.634323196249094</v>
       </c>
       <c r="N2" t="n">
-        <v>25.8876220849211</v>
+        <v>25.73118306329753</v>
       </c>
       <c r="O2" t="n">
-        <v>5.087988019337418</v>
+        <v>5.072591355835549</v>
       </c>
       <c r="P2" t="n">
-        <v>323.5358824587431</v>
+        <v>323.5353371784281</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29633,28 +29807,28 @@
         <v>0.127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3386884429623939</v>
+        <v>0.340625939591615</v>
       </c>
       <c r="J3" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K3" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2452911800261681</v>
+        <v>0.2498120282887215</v>
       </c>
       <c r="M3" t="n">
-        <v>3.270960015877074</v>
+        <v>3.260701378968031</v>
       </c>
       <c r="N3" t="n">
-        <v>20.48542610519031</v>
+        <v>20.37744389599498</v>
       </c>
       <c r="O3" t="n">
-        <v>4.526082865479852</v>
+        <v>4.514138222960722</v>
       </c>
       <c r="P3" t="n">
-        <v>310.4746180774532</v>
+        <v>310.454305490845</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29711,28 +29885,28 @@
         <v>0.0954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2484861534047916</v>
+        <v>0.2534771523536396</v>
       </c>
       <c r="J4" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K4" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L4" t="n">
-        <v>0.193603526648474</v>
+        <v>0.2009327150558358</v>
       </c>
       <c r="M4" t="n">
-        <v>2.901223029224334</v>
+        <v>2.907235212370664</v>
       </c>
       <c r="N4" t="n">
-        <v>14.92747993315676</v>
+        <v>14.94334614985203</v>
       </c>
       <c r="O4" t="n">
-        <v>3.863609702487657</v>
+        <v>3.865662446444597</v>
       </c>
       <c r="P4" t="n">
-        <v>312.3536680238867</v>
+        <v>312.3013366220188</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29789,28 +29963,28 @@
         <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2619221753995762</v>
+        <v>0.2636079120140256</v>
       </c>
       <c r="J5" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K5" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1977242418566694</v>
+        <v>0.2018390978592195</v>
       </c>
       <c r="M5" t="n">
-        <v>2.891499923698634</v>
+        <v>2.882736490030545</v>
       </c>
       <c r="N5" t="n">
-        <v>16.15678860786132</v>
+        <v>16.07087621474755</v>
       </c>
       <c r="O5" t="n">
-        <v>4.019550796775843</v>
+        <v>4.008849737112573</v>
       </c>
       <c r="P5" t="n">
-        <v>311.5553203644027</v>
+        <v>311.5376446467647</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29867,28 +30041,28 @@
         <v>0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.199729045238251</v>
+        <v>0.2017964584346957</v>
       </c>
       <c r="J6" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K6" t="n">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1777565883651478</v>
+        <v>0.182568085050136</v>
       </c>
       <c r="M6" t="n">
-        <v>2.481785271189922</v>
+        <v>2.476516097635815</v>
       </c>
       <c r="N6" t="n">
-        <v>10.72944731450629</v>
+        <v>10.68205951994488</v>
       </c>
       <c r="O6" t="n">
-        <v>3.27558350748478</v>
+        <v>3.268342013918506</v>
       </c>
       <c r="P6" t="n">
-        <v>314.4734665034811</v>
+        <v>314.4517994105912</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29945,28 +30119,28 @@
         <v>0.1233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1291416554212766</v>
+        <v>0.1295923905679246</v>
       </c>
       <c r="J7" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K7" t="n">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09762791472146881</v>
+        <v>0.09945334591749244</v>
       </c>
       <c r="M7" t="n">
-        <v>2.265097789351814</v>
+        <v>2.25351610932056</v>
       </c>
       <c r="N7" t="n">
-        <v>8.963230004714489</v>
+        <v>8.909370194835764</v>
       </c>
       <c r="O7" t="n">
-        <v>2.99386539522312</v>
+        <v>2.984856813121153</v>
       </c>
       <c r="P7" t="n">
-        <v>317.3339055997376</v>
+        <v>317.3291813041491</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30023,28 +30197,28 @@
         <v>0.106</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.000338505453123907</v>
+        <v>0.003300247685929157</v>
       </c>
       <c r="J8" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K8" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L8" t="n">
-        <v>6.260541349778492e-07</v>
+        <v>6.00020625188824e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.510777794817714</v>
+        <v>2.511700173549538</v>
       </c>
       <c r="N8" t="n">
-        <v>10.62345866762554</v>
+        <v>10.61544860127296</v>
       </c>
       <c r="O8" t="n">
-        <v>3.259364764432717</v>
+        <v>3.25813575550083</v>
       </c>
       <c r="P8" t="n">
-        <v>318.6689771939139</v>
+        <v>318.6308243298595</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30101,28 +30275,28 @@
         <v>0.1023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08615623573996166</v>
+        <v>-0.08083647835917612</v>
       </c>
       <c r="J9" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K9" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03984859721815848</v>
+        <v>0.03531790803528423</v>
       </c>
       <c r="M9" t="n">
-        <v>2.620875112363192</v>
+        <v>2.634483543687599</v>
       </c>
       <c r="N9" t="n">
-        <v>10.38118352574391</v>
+        <v>10.43858268153329</v>
       </c>
       <c r="O9" t="n">
-        <v>3.221984408054128</v>
+        <v>3.230879552309756</v>
       </c>
       <c r="P9" t="n">
-        <v>321.7925963477877</v>
+        <v>321.7368160316813</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30179,28 +30353,28 @@
         <v>0.1526</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09300284865896755</v>
+        <v>-0.08938017239216106</v>
       </c>
       <c r="J10" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K10" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03606753648114536</v>
+        <v>0.0337115639687765</v>
       </c>
       <c r="M10" t="n">
-        <v>2.84810215679583</v>
+        <v>2.850204016015702</v>
       </c>
       <c r="N10" t="n">
-        <v>13.41743138962764</v>
+        <v>13.3920720445052</v>
       </c>
       <c r="O10" t="n">
-        <v>3.662981216117227</v>
+        <v>3.659518007129518</v>
       </c>
       <c r="P10" t="n">
-        <v>324.534677487959</v>
+        <v>324.496693215604</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30257,28 +30431,28 @@
         <v>0.1109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1541287318136052</v>
+        <v>-0.1499500099237077</v>
       </c>
       <c r="J11" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K11" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1030663017759267</v>
+        <v>0.09875635978185116</v>
       </c>
       <c r="M11" t="n">
-        <v>2.768937134335925</v>
+        <v>2.77520726218616</v>
       </c>
       <c r="N11" t="n">
-        <v>11.99934698313245</v>
+        <v>12.0007297966405</v>
       </c>
       <c r="O11" t="n">
-        <v>3.464007358989361</v>
+        <v>3.464206950607959</v>
       </c>
       <c r="P11" t="n">
-        <v>324.1754119597716</v>
+        <v>324.1315963013098</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30335,28 +30509,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1975164799980482</v>
+        <v>-0.1976398115820928</v>
       </c>
       <c r="J12" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K12" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1166986679667593</v>
+        <v>0.118227368698729</v>
       </c>
       <c r="M12" t="n">
-        <v>3.319351542465949</v>
+        <v>3.303643916452254</v>
       </c>
       <c r="N12" t="n">
-        <v>17.13943159149374</v>
+        <v>17.03824949149741</v>
       </c>
       <c r="O12" t="n">
-        <v>4.139979660758461</v>
+        <v>4.127741451629136</v>
       </c>
       <c r="P12" t="n">
-        <v>315.9723224918569</v>
+        <v>315.9736225503546</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30413,28 +30587,28 @@
         <v>0.0591</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.213839016912902</v>
+        <v>-0.2142924624776862</v>
       </c>
       <c r="J13" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K13" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1241978550171621</v>
+        <v>0.1261514847981897</v>
       </c>
       <c r="M13" t="n">
-        <v>3.401981788936348</v>
+        <v>3.384295721245337</v>
       </c>
       <c r="N13" t="n">
-        <v>18.71597952572145</v>
+        <v>18.60351877608457</v>
       </c>
       <c r="O13" t="n">
-        <v>4.326196889384653</v>
+        <v>4.313179659611291</v>
       </c>
       <c r="P13" t="n">
-        <v>318.9427213420261</v>
+        <v>318.9474799147328</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30472,7 +30646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N489"/>
+  <dimension ref="A1:N492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65675,6 +65849,222 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-46.38427142311816,168.02901207761587</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-46.38405869328516,168.02816718579052</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-46.383928363305095,168.0272873104501</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-46.38374657611576,168.0264292823695</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-46.383610987557766,168.02555163920937</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-46.383458332574115,168.02468124205694</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-46.38331903687471,168.0238051722794</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-46.38319042842059,168.02292456406292</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-46.383050940044086,168.02203122031182</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-46.3830177017147,168.02111791421348</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>-46.38290103217593,168.02022605098952</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>-46.38291118787041,168.0193265773263</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-46.384267975404555,168.02901354134897</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-46.38405722801076,168.02816780788916</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-46.38392482941805,168.02728881083962</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-46.383751316683,168.0264272696101</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-46.38361383189008,168.02555043152665</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-46.383461607856745,168.02467985136175</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-46.38331567540987,168.0238065996035</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-46.383183446936535,168.02292752857238</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-46.38304342751813,168.02203319668195</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-46.38301133611957,168.02111849601448</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>-46.38288658842347,168.0202271426337</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>-46.382903382869614,168.01932716730903</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-46.384260562820245,168.02901668837447</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-46.38404981544611,168.02817095497588</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-46.38391827879809,168.02729159204884</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-46.38374407654391,168.0264303436425</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-46.38361107374966,168.02555160261292</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-46.38345928068225,168.0246808394873</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-46.38331162441376,168.02380831971175</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-46.383183446936535,168.02292752857238</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-46.38304342751813,168.02203319668195</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-46.38301133611957,168.02111849601448</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>-46.38288658842347,168.0202271426337</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>-46.382903382869614,168.01932716730903</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0535/nzd0535.xlsx
+++ b/data/nzd0535/nzd0535.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N492"/>
+  <dimension ref="A1:N494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24064,6 +24064,102 @@
       <c r="N492" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>326.64</v>
+      </c>
+      <c r="C493" t="n">
+        <v>319.04</v>
+      </c>
+      <c r="D493" t="n">
+        <v>321.47</v>
+      </c>
+      <c r="E493" t="n">
+        <v>318.61</v>
+      </c>
+      <c r="F493" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="G493" t="n">
+        <v>320.24</v>
+      </c>
+      <c r="H493" t="n">
+        <v>319.45</v>
+      </c>
+      <c r="I493" t="n">
+        <v>323.58</v>
+      </c>
+      <c r="J493" t="n">
+        <v>326.56</v>
+      </c>
+      <c r="K493" t="n">
+        <v>321.55</v>
+      </c>
+      <c r="L493" t="n">
+        <v>306.94</v>
+      </c>
+      <c r="M493" t="n">
+        <v>310.07</v>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>327.2</v>
+      </c>
+      <c r="C494" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="D494" t="n">
+        <v>321.71</v>
+      </c>
+      <c r="E494" t="n">
+        <v>319.32</v>
+      </c>
+      <c r="F494" t="n">
+        <v>321</v>
+      </c>
+      <c r="G494" t="n">
+        <v>321.17</v>
+      </c>
+      <c r="H494" t="n">
+        <v>320.17</v>
+      </c>
+      <c r="I494" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="J494" t="n">
+        <v>327.39</v>
+      </c>
+      <c r="K494" t="n">
+        <v>322.65</v>
+      </c>
+      <c r="L494" t="n">
+        <v>306.94</v>
+      </c>
+      <c r="M494" t="n">
+        <v>311.92</v>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24078,7 +24174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B548"/>
+  <dimension ref="A1:B550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29561,6 +29657,26 @@
       </c>
       <c r="B548" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -29729,28 +29845,28 @@
         <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.182799918777777</v>
+        <v>0.1815732551917904</v>
       </c>
       <c r="J2" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K2" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07058908171940725</v>
+        <v>0.07027265785622683</v>
       </c>
       <c r="M2" t="n">
-        <v>3.634323196249094</v>
+        <v>3.625039223977299</v>
       </c>
       <c r="N2" t="n">
-        <v>25.73118306329753</v>
+        <v>25.63686694094514</v>
       </c>
       <c r="O2" t="n">
-        <v>5.072591355835549</v>
+        <v>5.063286180036156</v>
       </c>
       <c r="P2" t="n">
-        <v>323.5353371784281</v>
+        <v>323.5482282452667</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29807,28 +29923,28 @@
         <v>0.127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.340625939591615</v>
+        <v>0.3402492955715909</v>
       </c>
       <c r="J3" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K3" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2498120282887215</v>
+        <v>0.2510816332163567</v>
       </c>
       <c r="M3" t="n">
-        <v>3.260701378968031</v>
+        <v>3.249438032400064</v>
       </c>
       <c r="N3" t="n">
-        <v>20.37744389599498</v>
+        <v>20.29579057247482</v>
       </c>
       <c r="O3" t="n">
-        <v>4.514138222960722</v>
+        <v>4.505084968396803</v>
       </c>
       <c r="P3" t="n">
-        <v>310.454305490845</v>
+        <v>310.4582634007782</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29885,28 +30001,28 @@
         <v>0.0954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2534771523536396</v>
+        <v>0.2553870130608278</v>
       </c>
       <c r="J4" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K4" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2009327150558358</v>
+        <v>0.204561059969028</v>
       </c>
       <c r="M4" t="n">
-        <v>2.907235212370664</v>
+        <v>2.904548576514798</v>
       </c>
       <c r="N4" t="n">
-        <v>14.94334614985203</v>
+        <v>14.90642387565474</v>
       </c>
       <c r="O4" t="n">
-        <v>3.865662446444597</v>
+        <v>3.860883820533161</v>
       </c>
       <c r="P4" t="n">
-        <v>312.3013366220188</v>
+        <v>312.2812636567554</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29963,28 +30079,28 @@
         <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2636079120140256</v>
+        <v>0.2638403938966702</v>
       </c>
       <c r="J5" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K5" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2018390978592195</v>
+        <v>0.2035740948819593</v>
       </c>
       <c r="M5" t="n">
-        <v>2.882736490030545</v>
+        <v>2.872516308206881</v>
       </c>
       <c r="N5" t="n">
-        <v>16.07087621474755</v>
+        <v>16.00653782915768</v>
       </c>
       <c r="O5" t="n">
-        <v>4.008849737112573</v>
+        <v>4.00081714517893</v>
       </c>
       <c r="P5" t="n">
-        <v>311.5376446467647</v>
+        <v>311.5351998970798</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30041,28 +30157,28 @@
         <v>0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2017964584346957</v>
+        <v>0.2023803823687263</v>
       </c>
       <c r="J6" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K6" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L6" t="n">
-        <v>0.182568085050136</v>
+        <v>0.1847486739822007</v>
       </c>
       <c r="M6" t="n">
-        <v>2.476516097635815</v>
+        <v>2.469254361075134</v>
       </c>
       <c r="N6" t="n">
-        <v>10.68205951994488</v>
+        <v>10.64133600846135</v>
       </c>
       <c r="O6" t="n">
-        <v>3.268342013918506</v>
+        <v>3.262106069468212</v>
       </c>
       <c r="P6" t="n">
-        <v>314.4517994105912</v>
+        <v>314.445664452497</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30119,28 +30235,28 @@
         <v>0.1233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1295923905679246</v>
+        <v>0.1294901727729833</v>
       </c>
       <c r="J7" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K7" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09945334591749244</v>
+        <v>0.1001123545420829</v>
       </c>
       <c r="M7" t="n">
-        <v>2.25351610932056</v>
+        <v>2.246231491595773</v>
       </c>
       <c r="N7" t="n">
-        <v>8.909370194835764</v>
+        <v>8.874080885417394</v>
       </c>
       <c r="O7" t="n">
-        <v>2.984856813121153</v>
+        <v>2.978939557194371</v>
       </c>
       <c r="P7" t="n">
-        <v>317.3291813041491</v>
+        <v>317.3302532134625</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30197,28 +30313,28 @@
         <v>0.106</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003300247685929157</v>
+        <v>0.004158931756987142</v>
       </c>
       <c r="J8" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K8" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L8" t="n">
-        <v>6.00020625188824e-05</v>
+        <v>9.609993429759989e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.511700173549538</v>
+        <v>2.505358194207507</v>
       </c>
       <c r="N8" t="n">
-        <v>10.61544860127296</v>
+        <v>10.57768736222529</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25813575550083</v>
+        <v>3.252335677974413</v>
       </c>
       <c r="P8" t="n">
-        <v>318.6308243298595</v>
+        <v>318.6217982136357</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30275,28 +30391,28 @@
         <v>0.1023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08083647835917612</v>
+        <v>-0.07738478169617664</v>
       </c>
       <c r="J9" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K9" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03531790803528423</v>
+        <v>0.03251150430096061</v>
       </c>
       <c r="M9" t="n">
-        <v>2.634483543687599</v>
+        <v>2.643218067291243</v>
       </c>
       <c r="N9" t="n">
-        <v>10.43858268153329</v>
+        <v>10.47398228991679</v>
       </c>
       <c r="O9" t="n">
-        <v>3.230879552309756</v>
+        <v>3.236353239360127</v>
       </c>
       <c r="P9" t="n">
-        <v>321.7368160316813</v>
+        <v>321.7005375343285</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30353,28 +30469,28 @@
         <v>0.1526</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08938017239216106</v>
+        <v>-0.08553091736882534</v>
       </c>
       <c r="J10" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K10" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0337115639687765</v>
+        <v>0.03101242840844043</v>
       </c>
       <c r="M10" t="n">
-        <v>2.850204016015702</v>
+        <v>2.859467997558219</v>
       </c>
       <c r="N10" t="n">
-        <v>13.3920720445052</v>
+        <v>13.43447374857877</v>
       </c>
       <c r="O10" t="n">
-        <v>3.659518007129518</v>
+        <v>3.665306774143029</v>
       </c>
       <c r="P10" t="n">
-        <v>324.496693215604</v>
+        <v>324.4562361943225</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30431,28 +30547,28 @@
         <v>0.1109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1499500099237077</v>
+        <v>-0.1483572325688729</v>
       </c>
       <c r="J11" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K11" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09875635978185116</v>
+        <v>0.09753395021639932</v>
       </c>
       <c r="M11" t="n">
-        <v>2.77520726218616</v>
+        <v>2.772838135548946</v>
       </c>
       <c r="N11" t="n">
-        <v>12.0007297966405</v>
+        <v>11.96973327000032</v>
       </c>
       <c r="O11" t="n">
-        <v>3.464206950607959</v>
+        <v>3.459730230812848</v>
       </c>
       <c r="P11" t="n">
-        <v>324.1315963013098</v>
+        <v>324.1148541545832</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30509,28 +30625,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1976398115820928</v>
+        <v>-0.2005392053001943</v>
       </c>
       <c r="J12" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K12" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L12" t="n">
-        <v>0.118227368698729</v>
+        <v>0.1219194229104694</v>
       </c>
       <c r="M12" t="n">
-        <v>3.303643916452254</v>
+        <v>3.305559601511001</v>
       </c>
       <c r="N12" t="n">
-        <v>17.03824949149741</v>
+        <v>17.02362399696054</v>
       </c>
       <c r="O12" t="n">
-        <v>4.127741451629136</v>
+        <v>4.125969461467274</v>
       </c>
       <c r="P12" t="n">
-        <v>315.9736225503546</v>
+        <v>316.0040949696769</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30587,28 +30703,28 @@
         <v>0.0591</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2142924624776862</v>
+        <v>-0.2159863365645094</v>
       </c>
       <c r="J13" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K13" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1261514847981897</v>
+        <v>0.1287739632230762</v>
       </c>
       <c r="M13" t="n">
-        <v>3.384295721245337</v>
+        <v>3.379069077850278</v>
       </c>
       <c r="N13" t="n">
-        <v>18.60351877608457</v>
+        <v>18.55014493831071</v>
       </c>
       <c r="O13" t="n">
-        <v>4.313179659611291</v>
+        <v>4.306987919452609</v>
       </c>
       <c r="P13" t="n">
-        <v>318.9474799147328</v>
+        <v>318.9652787997691</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30646,7 +30762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N492"/>
+  <dimension ref="A1:N494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66065,6 +66181,150 @@
         </is>
       </c>
     </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-46.38425047825768,168.02902096979136</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-46.38403619701305,168.0281767368304</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-46.383908366675584,168.02729580045613</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-46.38373494017776,168.0264342227773</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-46.38360081691479,168.0255559575888</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-46.38345143724219,168.02468416983575</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-46.383295851386,168.02381501715186</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-46.38318267121609,168.02292785796226</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-46.38305907124858,168.02202908118105</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-46.38299573592866,168.02111992183586</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>-46.382859136322345,168.02022921743327</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>-46.38288158269484,168.01932881519048</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-46.38425530505688,168.02901892056641</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-46.38403886898412,168.02817560241616</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-46.38391043529248,168.02729492217998</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-46.383741059819265,168.02643162448905</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-46.38360676415521,168.02555343243495</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-46.38345945306555,168.02468076629282</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-46.383302057167484,168.02381238209398</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-46.3831888769797,168.02292522284287</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-46.383066407009125,168.02202715131247</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-46.38300559811833,168.02111902045465</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>-46.382859136322345,168.02022921743327</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>-46.38289817953574,168.01932756063073</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
